--- a/resultados/Fiscalizacion_Web_DM_autotest-vih_24-08-2026.xlsx
+++ b/resultados/Fiscalizacion_Web_DM_autotest-vih_24-08-2026.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Búsquedas Marketplace" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hallazgos'!$A$1:$K$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hallazgos'!$A$1:$K$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,10 +35,14 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00A11B1B"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="001E6B1E"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -57,12 +61,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D7F0D7"/>
+        <fgColor rgb="00F8D7D7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF6CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D7F0D7"/>
       </patternFill>
     </fill>
   </fills>
@@ -92,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -107,6 +116,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -474,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -550,47 +562,39 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Autotest VIH</t>
+          <t>Test Rápido VIH MDcare</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>https://www.oraquick.cl/producto/oraquick-autoprueba-de-vih/</t>
+          <t>https://testrapidovih.cl/test-rapido-vih/</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Oraquick Autoprueba de VIH</t>
+          <t>Test Rapido VIH MDcare (Certificado) Enviamos a todo Chile</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>OraQuick.cl (tienda oficial, distribuida por Vitroscience SpA.)</t>
+          <t>testrapidovih.cl</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>SÍ</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>OraQuick® Autoprueba de VIH</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>DMDIV 001/23</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>REGISTRADO</t>
+          <t>NO REGISTRADO</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Sitio oficial de la marca en Chile, coincidencia directa por texto. Precio $13.990 CLP, botón de compra activo.</t>
+          <t>La marca MDcare NO figura entre los 5 autotest con registro sanitario vigente (OraQuick, CheckNOW, Panbio, Mylan, INSTI). El sitio se promociona como 'certificado' con 99,5% de efectividad y despacho a todo Chile. No se pudo abrir la ficha desde el entorno de búsqueda (el dominio no resolvió), así que el dato viene del listado del buscador: verificar manualmente antes de actuar. PRIORITARIO.</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr"/>
@@ -599,47 +603,39 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Autotest VIH</t>
+          <t>Test Rápido VIH Screening de 4ta generación</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>https://www.aprofa.cl/tienda/product/test-vih-autotest-oraquick/</t>
+          <t>https://www.autotestrapido.cl/test-rapido-vih-screening-de-4ta-generacion</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Test VIH Autotest Oraquick</t>
+          <t>Test Rápido VIH Screening de 4ta generación</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Aprofa (tienda online)</t>
+          <t>autotestrapido.cl</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>SÍ</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>OraQuick® Autoprueba de VIH</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>DMDIV 001/23</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>REGISTRADO</t>
+          <t>NO REGISTRADO</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>Coincidencia directa por texto (marca OraQuick). Publicación vigente pero sin stock al momento de la consulta.</t>
+          <t>Doble problema. Primero: ningún test de 4ta generación (Ag/Ab) figura en el listado de autotest, que solo ampara pruebas de anticuerpos para autodiagnóstico. Segundo: el sitio lo comercializa al público general como autotest con despacho el mismo día, cuando un Ag/Ab es de uso profesional. Sitio devolvió 403, sin verificación por imagen. PRIORITARIO.</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr"/>
@@ -648,47 +644,39 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Autotest VIH</t>
+          <t>Test Rápido Detección VIH (antígeno y anticuerpo)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>https://www.aprofa.cl/tienda/product/test-vih-autotest-mylan/</t>
+          <t>https://www.rappi.cl/p/test-rapido-deteccion-vih-466538</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Test VIH Autotest Mylan</t>
+          <t>Test Rápido Detección Vih</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Aprofa (tienda online)</t>
+          <t>Rappi Chile</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>SÍ</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Mylan HIV Self Test</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>DMDIV 004/23</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>REGISTRADO</t>
+          <t>NO REGISTRADO</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Coincidencia directa por texto (marca Mylan). Publicación vigente pero sin stock al momento de la consulta.</t>
+          <t>La ficha no declara marca ni fabricante. Describe detección de antígeno y anticuerpo en 'sangre, suero o plasma', que es una prueba de uso profesional, no un autotest: el manejo de suero o plasma requiere centrifugación. Ofertado al público en una app de delivery. Figura agotado, pero la publicación sigue activa.</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr"/>
@@ -697,22 +685,22 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Autotest VIH</t>
+          <t>OraQuick Autoprueba de VIH</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>https://www.cruzverde.cl/test-autoprueba-de-vih/542579.html</t>
+          <t>https://www.oraquick.cl/producto/oraquick-autoprueba-de-vih/</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Test Autoprueba De VIH</t>
+          <t>OraQuick Autoprueba de VIH</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Cruz Verde / Pharmaris Chile SpA.</t>
+          <t>OraQuick.cl (Vitroscience SpA.)</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -722,22 +710,22 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Mylan HIV Self Test</t>
+          <t>OraQuick® Autoprueba de VIH</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>DMDIV 004/23</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
+          <t>DMDIV 001/23</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>REGISTRADO</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>La ficha identifica al fabricante como Pharmaris, titular del registro de Mylan HIV Self Test. Precio $13.490 CLP.</t>
+          <t>Tienda oficial del titular del registro. Prueba oral.</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr"/>
@@ -746,22 +734,22 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Autotest VIH</t>
+          <t>Test VIH Autotest OraQuick</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>https://farmex.cl/products/autoprueba-de-vih-x-1-unidad</t>
+          <t>https://www.aprofa.cl/tienda/product/test-vih-autotest-oraquick/</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Test de VIH Autoprueba x 1 unidad</t>
+          <t>Test VIH Autotest OraQuick</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Farmex.cl</t>
+          <t>Aprofa</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -771,22 +759,22 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Mylan HIV Self Test</t>
+          <t>OraQuick® Autoprueba de VIH</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>DMDIV 004/23</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
+          <t>DMDIV 001/23</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>REGISTRADO</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Coincidencia directa por texto (marca Mylan). Publicación vigente, actualmente 'Agotado' pero visible y ofertada al público.</t>
+          <t>Aprofa es una ONG de salud sexual y reproductiva.</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr"/>
@@ -795,22 +783,22 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Autotest VIH</t>
+          <t>Test VIH Autotest Mylan</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>https://farmaciatudecision.cl/producto/autoprueba-de-vih-mylan-auto-test-vih/</t>
+          <t>https://www.aprofa.cl/tienda/product/test-vih-autotest-mylan/</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Autoprueba digital de VIH Digital MYLAN</t>
+          <t>Test VIH Autotest Mylan</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Farmacia Tu Decisión</t>
+          <t>Aprofa</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -828,14 +816,14 @@
           <t>DMDIV 004/23</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>REGISTRADO</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>Coincidencia directa por texto (marca Mylan). Publicación vigente, sin stock ni reposición programada según la ficha.</t>
+          <t>Titular Pharmaris Chile SpA. Prueba en sangre por punción digital.</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr"/>
@@ -844,22 +832,22 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Autotest VIH</t>
+          <t>Test Autoprueba de VIH (Mylan)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>https://salcobrand.cl/products/oraquick-autoprueba-de-vih-oral</t>
+          <t>https://www.cruzverde.cl/test-autoprueba-de-vih/542579.html</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Oraquick Autoprueba de VIH Oral</t>
+          <t>Test Autoprueba de VIH</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Salcobrand</t>
+          <t>Cruz Verde</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -869,22 +857,22 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>OraQuick® Autoprueba de VIH</t>
+          <t>Mylan HIV Self Test</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>DMDIV 001/23</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
+          <t>DMDIV 004/23</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>REGISTRADO</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Coincidencia directa por texto (marca OraQuick). Precio $14.499 CLP.</t>
+          <t>El título de la publicación no declara la marca; se identificó por la ficha, que menciona a Pharmaris Chile SpA como titular.</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr"/>
@@ -893,22 +881,22 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Autotest VIH</t>
+          <t>Test de VIH Autoprueba x 1 unidad (Mylan)</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://www.mercadofarma.cl/products/test-vih-mylan</t>
+          <t>https://farmex.cl/products/autoprueba-de-vih-x-1-unidad</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Test VIH Mylan</t>
+          <t>Test de VIH Autoprueba x 1 unidad</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Mercado Farma</t>
+          <t>Farmex</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -926,14 +914,14 @@
           <t>DMDIV 004/23</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>REGISTRADO</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Coincidencia directa por texto (marca Mylan). Precio $12.990 CLP, actualmente agotado en inventario.</t>
+          <t>Título genérico sin marca. Marca identificada por la descripción del producto.</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr"/>
@@ -942,22 +930,22 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Autotest VIH</t>
+          <t>Autoprueba de VIH Mylan Auto Test VIH</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>https://www.farmaciasahumada.cl/estuche-contiene-1-kit-autoprueba-vih-93214.html</t>
+          <t>https://farmaciatudecision.cl/producto/autoprueba-de-vih-mylan-auto-test-vih/</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Estuche Contiene 1 Kit Autoprueba Vih</t>
+          <t>Autoprueba de VIH Mylan Auto Test VIH</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Farmacias Ahumada</t>
+          <t>Farmacia Tu Decisión</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -967,29 +955,225 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>OraQuick® Autoprueba de VIH</t>
+          <t>Mylan HIV Self Test</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>DMDIV 001/23</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
+          <t>DMDIV 004/23</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>REGISTRADO</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Marca OraQuick identificada en el filtro de marca de la ficha de producto. Precio $10.834 CLP con descuento.</t>
+          <t>Marca declarada en el título.</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>OraQuick Autoprueba de VIH Oral</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>https://salcobrand.cl/products/oraquick-autoprueba-de-vih-oral</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>OraQuick Autoprueba de VIH Oral</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Salcobrand</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>OraQuick® Autoprueba de VIH</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>DMDIV 001/23</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Marca y vía de muestra declaradas en el título.</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr"/>
+      <c r="K11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Test VIH Mylan</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mercadofarma.cl/products/test-vih-mylan</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Test VIH Mylan</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Mercado Farma</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Mylan HIV Self Test</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>DMDIV 004/23</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Marca declarada en el título.</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr"/>
+      <c r="K12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>CheckNOW HIV Self Test (Abbott)</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>https://www.mercadofarma.cl/products/autotest-vih</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Autotest VIH</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Mercado Farma</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>CheckNOW™ HIV Self Test</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>DMDIV 002/23</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>El título de la publicación es solo 'Autotest VIH'; la marca CheckNOW de Abbott aparece en la descripción. Titular Abbott Laboratories de Chile Ltda.</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr"/>
+      <c r="K13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Estuche contiene 1 Kit Autoprueba VIH (OraQuick)</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.farmaciasahumada.cl/estuche-contiene-1-kit-autoprueba-vih-93214.html</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Estuche contiene 1 Kit Autoprueba VIH</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Farmacias Ahumada</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>OraQuick® Autoprueba de VIH</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>DMDIV 001/23</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Título genérico sin marca; identificada por la ficha del producto.</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr"/>
+      <c r="K14" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K10"/>
+  <autoFilter ref="A1:K14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1000,7 +1184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1057,30 +1241,63 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>https://listado.mercadolibre.cl/autotest-vih ; https://listado.mercadolibre.cl/test-rapido-vih</t>
+          <t>https://listado.mercadolibre.cl/autotest-vih</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>autotest VIH; test rápido VIH; prueba VIH</t>
+          <t>autotest vih / test rapido vih</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>All Test (9 publicaciones aprox.), Hightop (4), Aria, Accubiotech, Scanmed, Pro Touch, Panbio, OraQuick</t>
+          <t>no verificables, listado bloqueado</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>~75 resultados totales (búsqueda 'test vih'); ~34 en búsqueda de 15 minutos</t>
+          <t>no determinable</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Acceso directo a publicaciones individuales bloqueado por robots.txt (HTTP 403 confirmado en múltiples intentos, tanto en formato /up/ como articulo.mercadolibre.cl). Las marcas All Test, Hightop, Aria, Accubiotech, Scanmed y Pro Touch NO figuran en el listado ISP de Autotest VIH (que solo incluye OraQuick, CheckNOW, Panbio, Mylan e INSTI) — prioritarias para revisión manual del fiscalizador. IMPORTANTE: estas marcas corresponden típicamente a formato 'cassette' de uso profesional/clínico (no autodiagnóstico), por lo que además de verificar registro en la lista de Autotest VIH conviene cruzarlas contra la lista de 'Kits VIH uso profesional' antes de calificarlas, ya que podrían estar ofertándose al público general productos pensados para uso profesional. Se detectó también una publicación individual 'Test De Vih Certificado ISP, Detección desde los 14 días' (MLC-901548048) cuyo texto invoca certificación ISP; no se pudo verificar la marca por el bloqueo de acceso — revisar con prioridad por el reclamo de certificación.</t>
+          <t>403 en el listado y en las publicaciones individuales. Es la vía más probable de ingreso de autotest sin registro, porque no exige la trazabilidad de una farmacia. RECOMENDACIÓN: revisar manualmente filtrando por marca y contrastar contra los 5 autotest registrados (OraQuick, CheckNOW, Panbio, Mylan, INSTI). Cualquier otra marca es hallazgo.</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>(no aplica) Descartado por no ser venta de dispositivo</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.fastest.cl/examenes/vih/</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>test rapido vih 4ta generacion</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>AccuTell Rapid HIV Test</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>FASTEST Chile ofrece el test como SERVICIO en su centro de Providencia ($18.000), no como kit para llevar. Cita registro de dispositivo diagnóstico N° 982. Al no ser oferta de un dispositivo para autodiagnóstico, queda fuera de esta categoría. Se deja anotado porque usa un kit de 4ta generación y podría interesar a otra línea de fiscalización.</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/resultados/Fiscalizacion_Web_DM_autotest-vih_24-08-2026.xlsx
+++ b/resultados/Fiscalizacion_Web_DM_autotest-vih_24-08-2026.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="Hallazgos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Búsquedas Marketplace" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Anexo — sobre el tope" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Búsquedas Marketplace" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hallazgos'!$A$1:$K$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hallazgos'!$A$1:$K$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,6 +41,10 @@
     <font>
       <b val="1"/>
       <color rgb="001E6B1E"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="7">
@@ -101,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -121,6 +126,7 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -486,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1025,160 +1031,149 @@
       <c r="J11" s="4" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr"/>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Test VIH Mylan</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mercadofarma.cl/products/test-vih-mylan</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Test VIH Mylan</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Mercado Farma</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Mylan HIV Self Test</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>DMDIV 004/23</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>REGISTRADO</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Marca declarada en el título.</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr"/>
-      <c r="K12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>CheckNOW HIV Self Test (Abbott)</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>https://www.mercadofarma.cl/products/autotest-vih</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Autotest VIH</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Mercado Farma</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>CheckNOW™ HIV Self Test</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>DMDIV 002/23</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>REGISTRADO</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>El título de la publicación es solo 'Autotest VIH'; la marca CheckNOW de Abbott aparece en la descripción. Titular Abbott Laboratories de Chile Ltda.</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr"/>
-      <c r="K13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Estuche contiene 1 Kit Autoprueba VIH (OraQuick)</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.farmaciasahumada.cl/estuche-contiene-1-kit-autoprueba-vih-93214.html</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Estuche contiene 1 Kit Autoprueba VIH</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Farmacias Ahumada</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>OraQuick® Autoprueba de VIH</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>DMDIV 001/23</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>REGISTRADO</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>Título genérico sin marca; identificada por la ficha del producto.</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr"/>
-      <c r="K14" s="4" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K14"/>
+  <autoFilter ref="A1:K11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Nombre de DM ofertado</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Oferente</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Clasificación</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Observaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Test VIH Mylan</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mercadofarma.cl/products/test-vih-mylan</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Mercado Farma</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Marca declarada en el título.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>CheckNOW HIV Self Test (Abbott)</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.mercadofarma.cl/products/autotest-vih</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Mercado Farma</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>El título de la publicación es solo 'Autotest VIH'; la marca CheckNOW de Abbott aparece en la descripción. Titular Abbott Laboratories de Chile Ltda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Estuche contiene 1 Kit Autoprueba VIH (OraQuick)</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.farmaciasahumada.cl/estuche-contiene-1-kit-autoprueba-vih-93214.html</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Farmacias Ahumada</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Título genérico sin marca; identificada por la ficha del producto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Estas 3 ofertas se detectaron en la misma búsqueda pero quedaron fuera del reporte por el tope de 10 hallazgos. NO requieren revisión esta semana. Al no quedar registradas como evaluadas, vuelven a considerarse en la próxima corrida de la categoría.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/resultados/Fiscalizacion_Web_DM_autotest-vih_24-08-2026.xlsx
+++ b/resultados/Fiscalizacion_Web_DM_autotest-vih_24-08-2026.xlsx
@@ -8,11 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="Hallazgos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Anexo — sobre el tope" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Búsquedas Marketplace" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Búsquedas Marketplace" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hallazgos'!$A$1:$K$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hallazgos'!$A$1:$K$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,10 +40,6 @@
     <font>
       <b val="1"/>
       <color rgb="001E6B1E"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="9"/>
     </font>
   </fonts>
   <fills count="7">
@@ -106,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -126,7 +121,6 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -492,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1031,149 +1025,160 @@
       <c r="J11" s="4" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Test VIH Mylan</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mercadofarma.cl/products/test-vih-mylan</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Test VIH Mylan</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Mercado Farma</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Mylan HIV Self Test</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>DMDIV 004/23</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Marca declarada en el título.</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr"/>
+      <c r="K12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>CheckNOW HIV Self Test (Abbott)</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>https://www.mercadofarma.cl/products/autotest-vih</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Autotest VIH</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Mercado Farma</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>CheckNOW™ HIV Self Test</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>DMDIV 002/23</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>El título de la publicación es solo 'Autotest VIH'; la marca CheckNOW de Abbott aparece en la descripción. Titular Abbott Laboratories de Chile Ltda.</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr"/>
+      <c r="K13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Estuche contiene 1 Kit Autoprueba VIH (OraQuick)</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.farmaciasahumada.cl/estuche-contiene-1-kit-autoprueba-vih-93214.html</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Estuche contiene 1 Kit Autoprueba VIH</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Farmacias Ahumada</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>OraQuick® Autoprueba de VIH</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>DMDIV 001/23</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Título genérico sin marca; identificada por la ficha del producto.</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr"/>
+      <c r="K14" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K11"/>
+  <autoFilter ref="A1:K14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Nombre de DM ofertado</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Oferente</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Clasificación</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Observaciones</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Test VIH Mylan</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mercadofarma.cl/products/test-vih-mylan</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Mercado Farma</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>REGISTRADO</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Marca declarada en el título.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>CheckNOW HIV Self Test (Abbott)</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>https://www.mercadofarma.cl/products/autotest-vih</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>Mercado Farma</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>REGISTRADO</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>El título de la publicación es solo 'Autotest VIH'; la marca CheckNOW de Abbott aparece en la descripción. Titular Abbott Laboratories de Chile Ltda.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Estuche contiene 1 Kit Autoprueba VIH (OraQuick)</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.farmaciasahumada.cl/estuche-contiene-1-kit-autoprueba-vih-93214.html</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Farmacias Ahumada</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>REGISTRADO</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Título genérico sin marca; identificada por la ficha del producto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Estas 3 ofertas se detectaron en la misma búsqueda pero quedaron fuera del reporte por el tope de 10 hallazgos. NO requieren revisión esta semana. Al no quedar registradas como evaluadas, vuelven a considerarse en la próxima corrida de la categoría.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
